--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_60/per_file_predictions_epoch_60.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run6/epoch_60/per_file_predictions_epoch_60.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.7004,0.0988,0.1741,0.0526</t>
-  </si>
-  <si>
-    <t>0.0122,0.0085,0.0007,0.9934</t>
-  </si>
-  <si>
-    <t>0.7613,0.0090,0.0142,0.2336</t>
-  </si>
-  <si>
-    <t>0.0344,0.0072,0.0021,0.9848</t>
-  </si>
-  <si>
-    <t>0.9983,0.0007,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9909,0.0057,0.0002,0.0008</t>
-  </si>
-  <si>
-    <t>0.9926,0.0045,0.0009,0.0005</t>
-  </si>
-  <si>
-    <t>0.9943,0.0015,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.9897,0.0066,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9890,0.0104,0.0007,0.0007</t>
-  </si>
-  <si>
-    <t>0.9960,0.0004,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.7813,0.0332,0.1368,0.0368</t>
-  </si>
-  <si>
-    <t>0.1974,0.0283,0.8528,0.0104</t>
-  </si>
-  <si>
-    <t>0.2401,0.0547,0.8254,0.0006</t>
-  </si>
-  <si>
-    <t>0.1519,0.0316,0.8313,0.0257</t>
-  </si>
-  <si>
-    <t>0.8509,0.0151,0.0903,0.0180</t>
-  </si>
-  <si>
-    <t>0.0024,0.9938,0.0050,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.9900,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.3030,0.8165,0.0036,0.0014</t>
-  </si>
-  <si>
-    <t>0.0247,0.9742,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.0357,0.9612,0.0082,0.0007</t>
-  </si>
-  <si>
-    <t>0.4906,0.0154,0.1858,0.2604</t>
-  </si>
-  <si>
-    <t>0.3748,0.0174,0.5294,0.0825</t>
-  </si>
-  <si>
-    <t>0.0952,0.0168,0.8983,0.0037</t>
-  </si>
-  <si>
-    <t>0.4745,0.0156,0.6425,0.0048</t>
-  </si>
-  <si>
-    <t>0.0377,0.0035,0.9525,0.0206</t>
-  </si>
-  <si>
-    <t>0.0673,0.0077,0.9316,0.0037</t>
-  </si>
-  <si>
-    <t>0.0212,0.0033,0.9685,0.0082</t>
-  </si>
-  <si>
-    <t>0.3260,0.6831,0.0197,0.0269</t>
-  </si>
-  <si>
-    <t>0.6467,0.2121,0.2127,0.0081</t>
-  </si>
-  <si>
-    <t>0.0016,0.0045,0.9911,0.0089</t>
-  </si>
-  <si>
-    <t>0.0033,0.9846,0.0200,0.0005</t>
-  </si>
-  <si>
-    <t>0.8676,0.0821,0.0418,0.0143</t>
-  </si>
-  <si>
-    <t>0.5740,0.0741,0.4576,0.0127</t>
-  </si>
-  <si>
-    <t>0.2961,0.7104,0.0461,0.0006</t>
-  </si>
-  <si>
-    <t>0.0176,0.9529,0.1666,0.0079</t>
-  </si>
-  <si>
-    <t>0.0555,0.8416,0.0734,0.0256</t>
-  </si>
-  <si>
-    <t>0.0658,0.0518,0.8739,0.0695</t>
-  </si>
-  <si>
-    <t>0.0529,0.2110,0.8755,0.0131</t>
-  </si>
-  <si>
-    <t>0.0821,0.0053,0.9372,0.0053</t>
-  </si>
-  <si>
-    <t>0.0771,0.0804,0.8857,0.0019</t>
-  </si>
-  <si>
-    <t>0.0019,0.9818,0.0050,0.0002</t>
-  </si>
-  <si>
-    <t>0.0496,0.0764,0.8963,0.0106</t>
-  </si>
-  <si>
-    <t>0.0844,0.6417,0.0080,0.5394</t>
-  </si>
-  <si>
-    <t>0.0071,0.9750,0.0017,0.0101</t>
-  </si>
-  <si>
-    <t>0.0027,0.9874,0.0082,0.0023</t>
-  </si>
-  <si>
-    <t>0.0045,0.9719,0.0082,0.0225</t>
-  </si>
-  <si>
-    <t>0.0016,0.0265,0.9711,0.0211</t>
-  </si>
-  <si>
-    <t>0.0028,0.0512,0.9889,0.0017</t>
-  </si>
-  <si>
-    <t>0.0288,0.0072,0.9504,0.0204</t>
-  </si>
-  <si>
-    <t>0.0077,0.0014,0.9929,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.0048,0.9908,0.0047</t>
-  </si>
-  <si>
-    <t>0.0196,0.6271,0.6298,0.0084</t>
-  </si>
-  <si>
-    <t>0.9534,0.0650,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.9915,0.0040,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9891,0.0054,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.0055,0.0192,0.9880,0.0025</t>
-  </si>
-  <si>
-    <t>0.9917,0.0020,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.9957,0.0014,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.8775,0.1724,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.0015,0.8323,0.9623,0.0005</t>
-  </si>
-  <si>
-    <t>0.0462,0.0141,0.8850,0.0871</t>
-  </si>
-  <si>
-    <t>0.0136,0.0016,0.9500,0.0659</t>
-  </si>
-  <si>
-    <t>0.0055,0.8474,0.9183,0.0025</t>
-  </si>
-  <si>
-    <t>0.0015,0.0036,0.9825,0.0215</t>
-  </si>
-  <si>
-    <t>0.0877,0.8029,0.1107,0.0027</t>
-  </si>
-  <si>
-    <t>0.0270,0.9487,0.0097,0.0006</t>
-  </si>
-  <si>
-    <t>0.4049,0.0357,0.7462,0.0032</t>
-  </si>
-  <si>
-    <t>0.3389,0.3779,0.4293,0.0120</t>
-  </si>
-  <si>
-    <t>0.0080,0.0400,0.9617,0.0045</t>
-  </si>
-  <si>
-    <t>0.0071,0.5984,0.9370,0.0017</t>
-  </si>
-  <si>
-    <t>0.0033,0.3123,0.9777,0.0002</t>
-  </si>
-  <si>
-    <t>0.0021,0.9485,0.5067,0.0009</t>
-  </si>
-  <si>
-    <t>0.0027,0.9171,0.5946,0.0009</t>
-  </si>
-  <si>
-    <t>0.2005,0.0007,0.0062,0.8715</t>
-  </si>
-  <si>
-    <t>0.0011,0.0018,0.0002,0.9993</t>
-  </si>
-  <si>
-    <t>0.0017,0.0016,0.0010,0.9984</t>
-  </si>
-  <si>
-    <t>0.0113,0.0020,0.0006,0.9954</t>
-  </si>
-  <si>
-    <t>0.0102,0.0013,0.0011,0.9955</t>
-  </si>
-  <si>
-    <t>0.0032,0.0033,0.0001,0.9985</t>
-  </si>
-  <si>
-    <t>0.0009,0.8894,0.9557,0.0002</t>
-  </si>
-  <si>
-    <t>0.0020,0.7130,0.9582,0.0003</t>
-  </si>
-  <si>
-    <t>0.0198,0.2674,0.8710,0.0029</t>
-  </si>
-  <si>
-    <t>0.0086,0.8323,0.7844,0.0025</t>
-  </si>
-  <si>
-    <t>0.0017,0.8667,0.8600,0.0004</t>
-  </si>
-  <si>
-    <t>0.0076,0.5980,0.8795,0.0013</t>
-  </si>
-  <si>
-    <t>0.9934,0.0024,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9900,0.0103,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9834,0.0209,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9931,0.0007,0.0000,0.0026</t>
-  </si>
-  <si>
-    <t>0.9892,0.0078,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9967,0.0014,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9960,0.0017,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9953,0.0032,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9967,0.0013,0.0001,0.0004</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.8183,0.0335,0.0256,0.0835</t>
+  </si>
+  <si>
+    <t>0.0099,0.0010,0.0005,0.9964</t>
+  </si>
+  <si>
+    <t>0.5272,0.0048,0.0034,0.6313</t>
+  </si>
+  <si>
+    <t>0.0974,0.0020,0.0026,0.9608</t>
+  </si>
+  <si>
+    <t>0.9980,0.0004,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9974,0.0007,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9934,0.0012,0.0001,0.0021</t>
+  </si>
+  <si>
+    <t>0.9978,0.0005,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9855,0.0209,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9927,0.0048,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9952,0.0004,0.0000,0.0021</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.7202,0.0859,0.1716,0.0324</t>
+  </si>
+  <si>
+    <t>0.2068,0.0194,0.8692,0.0029</t>
+  </si>
+  <si>
+    <t>0.3679,0.0126,0.8105,0.0005</t>
+  </si>
+  <si>
+    <t>0.2285,0.0404,0.7696,0.0047</t>
+  </si>
+  <si>
+    <t>0.7340,0.0702,0.1964,0.0384</t>
+  </si>
+  <si>
+    <t>0.0107,0.9819,0.0045,0.0007</t>
+  </si>
+  <si>
+    <t>0.0609,0.9426,0.0107,0.0046</t>
+  </si>
+  <si>
+    <t>0.3016,0.7586,0.0232,0.0042</t>
+  </si>
+  <si>
+    <t>0.0630,0.9501,0.0025,0.0021</t>
+  </si>
+  <si>
+    <t>0.0272,0.9784,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.4649,0.0281,0.5835,0.0063</t>
+  </si>
+  <si>
+    <t>0.6241,0.0440,0.3284,0.0374</t>
+  </si>
+  <si>
+    <t>0.0078,0.0023,0.9892,0.0021</t>
+  </si>
+  <si>
+    <t>0.3692,0.0094,0.7837,0.0013</t>
+  </si>
+  <si>
+    <t>0.0553,0.0032,0.9497,0.0065</t>
+  </si>
+  <si>
+    <t>0.0716,0.0026,0.9553,0.0022</t>
+  </si>
+  <si>
+    <t>0.0031,0.0017,0.9921,0.0029</t>
+  </si>
+  <si>
+    <t>0.6040,0.3764,0.0362,0.0012</t>
+  </si>
+  <si>
+    <t>0.8079,0.0970,0.1004,0.0074</t>
+  </si>
+  <si>
+    <t>0.0035,0.0046,0.9862,0.0102</t>
+  </si>
+  <si>
+    <t>0.0112,0.8681,0.2449,0.0012</t>
+  </si>
+  <si>
+    <t>0.7637,0.1351,0.1228,0.0107</t>
+  </si>
+  <si>
+    <t>0.3188,0.0295,0.7842,0.0045</t>
+  </si>
+  <si>
+    <t>0.7314,0.3507,0.0259,0.0020</t>
+  </si>
+  <si>
+    <t>0.0098,0.9595,0.1044,0.0020</t>
+  </si>
+  <si>
+    <t>0.0057,0.9214,0.0599,0.0317</t>
+  </si>
+  <si>
+    <t>0.0316,0.0866,0.9357,0.0283</t>
+  </si>
+  <si>
+    <t>0.0338,0.4455,0.8251,0.0044</t>
+  </si>
+  <si>
+    <t>0.3726,0.0028,0.7859,0.0022</t>
+  </si>
+  <si>
+    <t>0.0748,0.4061,0.7523,0.0067</t>
+  </si>
+  <si>
+    <t>0.0041,0.9594,0.0154,0.0041</t>
+  </si>
+  <si>
+    <t>0.0069,0.0052,0.9895,0.0019</t>
+  </si>
+  <si>
+    <t>0.0350,0.7240,0.0045,0.6370</t>
+  </si>
+  <si>
+    <t>0.0065,0.9313,0.0007,0.1153</t>
+  </si>
+  <si>
+    <t>0.0089,0.9740,0.0126,0.0049</t>
+  </si>
+  <si>
+    <t>0.0096,0.9777,0.0221,0.0021</t>
+  </si>
+  <si>
+    <t>0.0058,0.4842,0.9439,0.0058</t>
+  </si>
+  <si>
+    <t>0.0008,0.1166,0.9914,0.0010</t>
+  </si>
+  <si>
+    <t>0.0517,0.0038,0.9570,0.0030</t>
+  </si>
+  <si>
+    <t>0.0898,0.0007,0.9640,0.0005</t>
+  </si>
+  <si>
+    <t>0.0025,0.0076,0.9875,0.0104</t>
+  </si>
+  <si>
+    <t>0.0053,0.0259,0.9663,0.0203</t>
+  </si>
+  <si>
+    <t>0.9664,0.0427,0.0015,0.0012</t>
+  </si>
+  <si>
+    <t>0.9683,0.0152,0.0145,0.0011</t>
+  </si>
+  <si>
+    <t>0.9853,0.0057,0.0015,0.0020</t>
+  </si>
+  <si>
+    <t>0.0004,0.0150,0.9976,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0012,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9885,0.0134,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9317,0.1056,0.0034,0.0010</t>
+  </si>
+  <si>
+    <t>0.0025,0.8143,0.9375,0.0006</t>
+  </si>
+  <si>
+    <t>0.0033,0.0143,0.9756,0.0170</t>
+  </si>
+  <si>
+    <t>0.0047,0.0082,0.9746,0.0344</t>
+  </si>
+  <si>
+    <t>0.0023,0.9305,0.8508,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.0033,0.9904,0.0054</t>
+  </si>
+  <si>
+    <t>0.0760,0.8176,0.1341,0.0009</t>
+  </si>
+  <si>
+    <t>0.0510,0.9367,0.0018,0.0008</t>
+  </si>
+  <si>
+    <t>0.7324,0.0292,0.3560,0.0146</t>
+  </si>
+  <si>
+    <t>0.6647,0.2079,0.1028,0.1034</t>
+  </si>
+  <si>
+    <t>0.0122,0.0329,0.9718,0.0018</t>
+  </si>
+  <si>
+    <t>0.0045,0.7817,0.9092,0.0006</t>
+  </si>
+  <si>
+    <t>0.0050,0.7348,0.8360,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.9733,0.2086,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.9154,0.6909,0.0005</t>
+  </si>
+  <si>
+    <t>0.0041,0.0033,0.0283,0.9901</t>
+  </si>
+  <si>
+    <t>0.0004,0.0123,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0050,0.0011,0.0001,0.9984</t>
+  </si>
+  <si>
+    <t>0.0063,0.0020,0.0009,0.9966</t>
+  </si>
+  <si>
+    <t>0.0042,0.0079,0.0014,0.9961</t>
+  </si>
+  <si>
+    <t>0.0032,0.0022,0.0004,0.9982</t>
+  </si>
+  <si>
+    <t>0.0004,0.9599,0.9372,0.0002</t>
+  </si>
+  <si>
+    <t>0.0036,0.5969,0.9693,0.0003</t>
+  </si>
+  <si>
+    <t>0.0164,0.3890,0.8033,0.0004</t>
+  </si>
+  <si>
+    <t>0.0092,0.2703,0.9469,0.0038</t>
+  </si>
+  <si>
+    <t>0.0046,0.9240,0.4332,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.8874,0.4196,0.0004</t>
+  </si>
+  <si>
+    <t>0.9940,0.0038,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9931,0.0043,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9325,0.1140,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.9948,0.0020,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9878,0.0022,0.0001,0.0036</t>
+  </si>
+  <si>
+    <t>0.9964,0.0009,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9856,0.0144,0.0010,0.0007</t>
+  </si>
+  <si>
+    <t>0.9854,0.0140,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9968,0.0013,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9952,0.0017,0.0002,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0011,0.0000,0.0001</t>
   </si>
   <si>
     <t>0.9978,0.0002,0.0000,0.0006</t>
   </si>
   <si>
-    <t>0.9979,0.0005,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9951,0.0019,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9977,0.0003,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9944,0.0025,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9952,0.0019,0.0002,0.0006</t>
-  </si>
-  <si>
-    <t>0.0488,0.0040,0.9425,0.0224</t>
-  </si>
-  <si>
-    <t>0.0927,0.0332,0.9061,0.0024</t>
-  </si>
-  <si>
-    <t>0.8390,0.0043,0.1865,0.0054</t>
-  </si>
-  <si>
-    <t>0.0029,0.0023,0.9940,0.0010</t>
-  </si>
-  <si>
-    <t>0.0046,0.9892,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.0141,0.9780,0.0102,0.0004</t>
-  </si>
-  <si>
-    <t>0.0564,0.9540,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.0710,0.9452,0.0029,0.0015</t>
-  </si>
-  <si>
-    <t>0.0506,0.9432,0.0143,0.0022</t>
-  </si>
-  <si>
-    <t>0.0070,0.9844,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.3083,0.7289,0.0320,0.0013</t>
-  </si>
-  <si>
-    <t>0.6270,0.1909,0.2352,0.0183</t>
-  </si>
-  <si>
-    <t>0.3300,0.0082,0.7709,0.0076</t>
-  </si>
-  <si>
-    <t>0.2626,0.6176,0.0744,0.0539</t>
-  </si>
-  <si>
-    <t>0.6399,0.0537,0.3949,0.0048</t>
-  </si>
-  <si>
-    <t>0.1261,0.3293,0.0495,0.8307</t>
-  </si>
-  <si>
-    <t>0.0295,0.9601,0.0053,0.0029</t>
-  </si>
-  <si>
-    <t>0.0063,0.9692,0.0105,0.0154</t>
-  </si>
-  <si>
-    <t>0.0471,0.8872,0.0064,0.1052</t>
-  </si>
-  <si>
-    <t>0.0176,0.9173,0.3950,0.0103</t>
-  </si>
-  <si>
-    <t>0.0057,0.9873,0.0096,0.0010</t>
-  </si>
-  <si>
-    <t>0.8104,0.2335,0.0171,0.0004</t>
-  </si>
-  <si>
-    <t>0.5080,0.5965,0.0164,0.0027</t>
-  </si>
-  <si>
-    <t>0.9474,0.0131,0.0002,0.0118</t>
-  </si>
-  <si>
-    <t>0.9915,0.0028,0.0005,0.0013</t>
-  </si>
-  <si>
-    <t>0.9822,0.0043,0.0007,0.0062</t>
-  </si>
-  <si>
-    <t>0.9807,0.0098,0.0027,0.0022</t>
-  </si>
-  <si>
-    <t>0.9921,0.0002,0.0000,0.0059</t>
-  </si>
-  <si>
-    <t>0.9686,0.0144,0.0098,0.0025</t>
-  </si>
-  <si>
-    <t>0.9813,0.0034,0.0013,0.0065</t>
-  </si>
-  <si>
-    <t>0.9887,0.0007,0.0005,0.0050</t>
-  </si>
-  <si>
-    <t>0.0112,0.3620,0.9535,0.0034</t>
-  </si>
-  <si>
-    <t>0.0007,0.8172,0.9596,0.0000</t>
-  </si>
-  <si>
-    <t>0.0079,0.1511,0.9626,0.0055</t>
-  </si>
-  <si>
-    <t>0.0739,0.0966,0.8582,0.0012</t>
-  </si>
-  <si>
-    <t>0.7703,0.1225,0.0404,0.0205</t>
-  </si>
-  <si>
-    <t>0.7300,0.0728,0.2119,0.0260</t>
-  </si>
-  <si>
-    <t>0.3431,0.0018,0.8385,0.0017</t>
-  </si>
-  <si>
-    <t>0.6400,0.3546,0.0226,0.0135</t>
-  </si>
-  <si>
-    <t>0.1933,0.0007,0.0007,0.9328</t>
-  </si>
-  <si>
-    <t>0.0004,0.0010,0.0020,0.9991</t>
-  </si>
-  <si>
-    <t>0.0033,0.0007,0.0040,0.9966</t>
-  </si>
-  <si>
-    <t>0.0057,0.0004,0.0022,0.9965</t>
-  </si>
-  <si>
-    <t>0.0027,0.8416,0.8965,0.0012</t>
-  </si>
-  <si>
-    <t>0.9844,0.0117,0.0008,0.0014</t>
-  </si>
-  <si>
-    <t>0.1907,0.8466,0.0072,0.0063</t>
-  </si>
-  <si>
-    <t>0.9889,0.0050,0.0007,0.0012</t>
-  </si>
-  <si>
-    <t>0.6889,0.4842,0.0061,0.0018</t>
-  </si>
-  <si>
-    <t>0.9706,0.0056,0.0109,0.0041</t>
-  </si>
-  <si>
-    <t>0.1610,0.0012,0.0061,0.9138</t>
-  </si>
-  <si>
-    <t>0.9811,0.0037,0.0057,0.0025</t>
-  </si>
-  <si>
-    <t>0.0024,0.0201,0.9802,0.0178</t>
-  </si>
-  <si>
-    <t>0.9328,0.0003,0.0088,0.0273</t>
-  </si>
-  <si>
-    <t>0.9728,0.0046,0.0047,0.0060</t>
-  </si>
-  <si>
-    <t>0.0997,0.8975,0.0160,0.0052</t>
-  </si>
-  <si>
-    <t>0.7101,0.3059,0.0146,0.0102</t>
-  </si>
-  <si>
-    <t>0.8379,0.1405,0.0504,0.0042</t>
-  </si>
-  <si>
-    <t>0.3545,0.6639,0.0137,0.0133</t>
-  </si>
-  <si>
-    <t>0.8001,0.1383,0.0725,0.0067</t>
-  </si>
-  <si>
-    <t>0.8967,0.0730,0.0216,0.0080</t>
-  </si>
-  <si>
-    <t>0.9980,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9847,0.0072,0.0004,0.0023</t>
-  </si>
-  <si>
-    <t>0.9924,0.0023,0.0010,0.0012</t>
-  </si>
-  <si>
-    <t>0.9910,0.0017,0.0005,0.0026</t>
-  </si>
-  <si>
-    <t>0.9927,0.0015,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.9932,0.0018,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9914,0.0011,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9936,0.0014,0.0001,0.0015</t>
-  </si>
-  <si>
-    <t>0.5938,0.5370,0.0133,0.0049</t>
-  </si>
-  <si>
-    <t>0.5327,0.5738,0.0170,0.0012</t>
-  </si>
-  <si>
-    <t>0.8228,0.3221,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.5292,0.3267,0.2179,0.0055</t>
-  </si>
-  <si>
-    <t>0.8760,0.2028,0.0022,0.0018</t>
-  </si>
-  <si>
-    <t>0.9801,0.0065,0.0051,0.0028</t>
-  </si>
-  <si>
-    <t>0.9799,0.0156,0.0012,0.0014</t>
-  </si>
-  <si>
-    <t>0.9612,0.0420,0.0008,0.0020</t>
-  </si>
-  <si>
-    <t>0.0005,0.0090,0.9963,0.0019</t>
-  </si>
-  <si>
-    <t>0.8561,0.2591,0.0032,0.0005</t>
-  </si>
-  <si>
-    <t>0.0151,0.0143,0.9820,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.0426,0.9810,0.0031</t>
-  </si>
-  <si>
-    <t>0.0773,0.0119,0.8913,0.0337</t>
-  </si>
-  <si>
-    <t>0.0102,0.0548,0.9649,0.0017</t>
-  </si>
-  <si>
-    <t>0.0086,0.0028,0.9834,0.0049</t>
-  </si>
-  <si>
-    <t>0.0054,0.0030,0.9912,0.0013</t>
-  </si>
-  <si>
-    <t>0.0173,0.0058,0.9841,0.0003</t>
-  </si>
-  <si>
-    <t>0.3511,0.1127,0.5949,0.1085</t>
-  </si>
-  <si>
-    <t>0.2544,0.0223,0.8305,0.0003</t>
-  </si>
-  <si>
-    <t>0.7121,0.0524,0.2868,0.0065</t>
-  </si>
-  <si>
-    <t>0.3321,0.0574,0.6923,0.0030</t>
-  </si>
-  <si>
-    <t>0.3041,0.2499,0.4061,0.0031</t>
-  </si>
-  <si>
-    <t>0.8147,0.0195,0.1776,0.0011</t>
-  </si>
-  <si>
-    <t>0.6135,0.1633,0.1204,0.1051</t>
-  </si>
-  <si>
-    <t>0.1804,0.0948,0.8422,0.0041</t>
-  </si>
-  <si>
-    <t>0.7053,0.4530,0.0058,0.0008</t>
-  </si>
-  <si>
-    <t>0.2598,0.8300,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.4812,0.7050,0.0039,0.0011</t>
-  </si>
-  <si>
-    <t>0.9721,0.0441,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.6420,0.4259,0.0005,0.0030</t>
-  </si>
-  <si>
-    <t>0.6483,0.1743,0.1916,0.0233</t>
-  </si>
-  <si>
-    <t>0.8715,0.0059,0.1238,0.0039</t>
-  </si>
-  <si>
-    <t>0.8554,0.0255,0.0789,0.0090</t>
-  </si>
-  <si>
-    <t>0.5869,0.0075,0.5641,0.0045</t>
-  </si>
-  <si>
-    <t>0.8686,0.0112,0.0780,0.0176</t>
-  </si>
-  <si>
-    <t>0.0191,0.0119,0.9475,0.0391</t>
-  </si>
-  <si>
-    <t>0.0674,0.4685,0.6363,0.0114</t>
-  </si>
-  <si>
-    <t>0.0890,0.2021,0.8465,0.0068</t>
-  </si>
-  <si>
-    <t>0.0785,0.0294,0.8876,0.0127</t>
-  </si>
-  <si>
-    <t>0.0364,0.5836,0.5385,0.0033</t>
-  </si>
-  <si>
-    <t>0.9924,0.0020,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9919,0.0072,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.9801,0.0011,0.0000,0.0158</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9840,0.0075,0.0005,0.0023</t>
-  </si>
-  <si>
-    <t>0.9915,0.0051,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.9799,0.0110,0.0013,0.0029</t>
-  </si>
-  <si>
-    <t>0.9936,0.0018,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.0554,0.0238,0.9548,0.0008</t>
-  </si>
-  <si>
-    <t>0.1639,0.3786,0.6875,0.0131</t>
-  </si>
-  <si>
-    <t>0.8453,0.0644,0.0386,0.0273</t>
-  </si>
-  <si>
-    <t>0.0117,0.0257,0.9668,0.0078</t>
-  </si>
-  <si>
-    <t>0.0031,0.0109,0.9870,0.0040</t>
-  </si>
-  <si>
-    <t>0.1472,0.0964,0.7443,0.0012</t>
-  </si>
-  <si>
-    <t>0.0035,0.0043,0.9918,0.0015</t>
-  </si>
-  <si>
-    <t>0.0259,0.0061,0.9668,0.0039</t>
-  </si>
-  <si>
-    <t>0.0190,0.0194,0.9718,0.0046</t>
-  </si>
-  <si>
-    <t>0.0073,0.0200,0.9866,0.0014</t>
-  </si>
-  <si>
-    <t>0.1075,0.1411,0.8115,0.0189</t>
-  </si>
-  <si>
-    <t>0.7200,0.0124,0.2843,0.0190</t>
-  </si>
-  <si>
-    <t>0.7947,0.0101,0.2804,0.0013</t>
-  </si>
-  <si>
-    <t>0.8667,0.0263,0.0841,0.0032</t>
-  </si>
-  <si>
-    <t>0.9900,0.0175,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0026,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0040,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.9827,0.0172,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9908,0.0006,0.0001,0.0051</t>
-  </si>
-  <si>
-    <t>0.9939,0.0056,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0018,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9908,0.0036,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.1432,0.1116,0.7508,0.0066</t>
-  </si>
-  <si>
-    <t>0.0018,0.0126,0.9938,0.0006</t>
-  </si>
-  <si>
-    <t>0.0646,0.2374,0.7663,0.0211</t>
-  </si>
-  <si>
-    <t>0.0925,0.1766,0.6316,0.0015</t>
-  </si>
-  <si>
-    <t>0.0299,0.0042,0.9636,0.0056</t>
-  </si>
-  <si>
-    <t>0.0129,0.0068,0.7698,0.6158</t>
-  </si>
-  <si>
-    <t>0.1135,0.0033,0.9287,0.0016</t>
-  </si>
-  <si>
-    <t>0.1507,0.4584,0.4000,0.0433</t>
-  </si>
-  <si>
-    <t>0.7517,0.0004,0.0027,0.2990</t>
-  </si>
-  <si>
-    <t>0.0197,0.0134,0.0006,0.9904</t>
-  </si>
-  <si>
-    <t>0.0133,0.0012,0.0005,0.9957</t>
-  </si>
-  <si>
-    <t>0.0035,0.0003,0.0002,0.9988</t>
-  </si>
-  <si>
-    <t>0.0051,0.0011,0.0003,0.9980</t>
-  </si>
-  <si>
-    <t>0.7486,0.0456,0.0655,0.1457</t>
+    <t>0.9945,0.0018,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9952,0.0020,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9964,0.0006,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9923,0.0042,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.0690,0.0047,0.9570,0.0025</t>
+  </si>
+  <si>
+    <t>0.1105,0.0124,0.9114,0.0059</t>
+  </si>
+  <si>
+    <t>0.8505,0.0036,0.1439,0.0096</t>
+  </si>
+  <si>
+    <t>0.0888,0.0087,0.9083,0.0180</t>
+  </si>
+  <si>
+    <t>0.0057,0.9905,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.1619,0.8497,0.0209,0.0029</t>
+  </si>
+  <si>
+    <t>0.0249,0.9711,0.0019,0.0008</t>
+  </si>
+  <si>
+    <t>0.6130,0.5435,0.0062,0.0008</t>
+  </si>
+  <si>
+    <t>0.0219,0.9724,0.0027,0.0013</t>
+  </si>
+  <si>
+    <t>0.0010,0.9965,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.2159,0.8395,0.0068,0.0004</t>
+  </si>
+  <si>
+    <t>0.4757,0.2798,0.2813,0.0146</t>
+  </si>
+  <si>
+    <t>0.2581,0.0029,0.8718,0.0025</t>
+  </si>
+  <si>
+    <t>0.6741,0.0640,0.2559,0.0160</t>
+  </si>
+  <si>
+    <t>0.8202,0.0087,0.2227,0.0026</t>
+  </si>
+  <si>
+    <t>0.0804,0.2321,0.0127,0.8899</t>
+  </si>
+  <si>
+    <t>0.0061,0.9853,0.0028,0.0016</t>
+  </si>
+  <si>
+    <t>0.0020,0.9720,0.0021,0.0599</t>
+  </si>
+  <si>
+    <t>0.0179,0.8982,0.0079,0.1705</t>
+  </si>
+  <si>
+    <t>0.0031,0.8359,0.8593,0.0046</t>
+  </si>
+  <si>
+    <t>0.0538,0.9391,0.0604,0.0015</t>
+  </si>
+  <si>
+    <t>0.7703,0.1984,0.0764,0.0014</t>
+  </si>
+  <si>
+    <t>0.3712,0.6451,0.0479,0.0008</t>
+  </si>
+  <si>
+    <t>0.9795,0.0050,0.0027,0.0036</t>
+  </si>
+  <si>
+    <t>0.9881,0.0031,0.0012,0.0022</t>
+  </si>
+  <si>
+    <t>0.9887,0.0004,0.0000,0.0101</t>
+  </si>
+  <si>
+    <t>0.9859,0.0021,0.0009,0.0043</t>
+  </si>
+  <si>
+    <t>0.9940,0.0005,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9401,0.0120,0.0301,0.0090</t>
+  </si>
+  <si>
+    <t>0.9934,0.0002,0.0001,0.0050</t>
+  </si>
+  <si>
+    <t>0.9874,0.0046,0.0011,0.0024</t>
+  </si>
+  <si>
+    <t>0.0083,0.4849,0.9531,0.0022</t>
+  </si>
+  <si>
+    <t>0.0032,0.5419,0.9382,0.0001</t>
+  </si>
+  <si>
+    <t>0.0215,0.2657,0.9221,0.0017</t>
+  </si>
+  <si>
+    <t>0.0567,0.1549,0.7779,0.0003</t>
+  </si>
+  <si>
+    <t>0.8556,0.0695,0.0273,0.0105</t>
+  </si>
+  <si>
+    <t>0.8325,0.0488,0.0756,0.0142</t>
+  </si>
+  <si>
+    <t>0.2723,0.0072,0.8424,0.0066</t>
+  </si>
+  <si>
+    <t>0.4503,0.4346,0.1458,0.0163</t>
+  </si>
+  <si>
+    <t>0.1692,0.0007,0.0004,0.9479</t>
+  </si>
+  <si>
+    <t>0.0011,0.0014,0.0019,0.9985</t>
+  </si>
+  <si>
+    <t>0.0016,0.0054,0.0010,0.9982</t>
+  </si>
+  <si>
+    <t>0.0324,0.0031,0.0008,0.9878</t>
+  </si>
+  <si>
+    <t>0.0018,0.6119,0.9782,0.0006</t>
+  </si>
+  <si>
+    <t>0.9866,0.0057,0.0018,0.0014</t>
+  </si>
+  <si>
+    <t>0.2599,0.7611,0.0213,0.0029</t>
+  </si>
+  <si>
+    <t>0.9888,0.0071,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.6016,0.4907,0.0218,0.0019</t>
+  </si>
+  <si>
+    <t>0.9883,0.0020,0.0020,0.0015</t>
+  </si>
+  <si>
+    <t>0.6671,0.0516,0.0275,0.2189</t>
+  </si>
+  <si>
+    <t>0.9785,0.0027,0.0015,0.0069</t>
+  </si>
+  <si>
+    <t>0.0033,0.0103,0.9824,0.0152</t>
+  </si>
+  <si>
+    <t>0.7686,0.0004,0.0035,0.2842</t>
+  </si>
+  <si>
+    <t>0.9466,0.0009,0.0044,0.0281</t>
+  </si>
+  <si>
+    <t>0.3651,0.6319,0.0341,0.0066</t>
+  </si>
+  <si>
+    <t>0.9329,0.0582,0.0018,0.0046</t>
+  </si>
+  <si>
+    <t>0.8793,0.0698,0.0445,0.0094</t>
+  </si>
+  <si>
+    <t>0.3772,0.6119,0.0832,0.0081</t>
+  </si>
+  <si>
+    <t>0.7291,0.3153,0.0395,0.0090</t>
+  </si>
+  <si>
+    <t>0.6657,0.3990,0.0306,0.0115</t>
+  </si>
+  <si>
+    <t>0.9853,0.0026,0.0005,0.0067</t>
+  </si>
+  <si>
+    <t>0.9905,0.0015,0.0001,0.0031</t>
+  </si>
+  <si>
+    <t>0.9940,0.0017,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9881,0.0018,0.0014,0.0033</t>
+  </si>
+  <si>
+    <t>0.9836,0.0062,0.0021,0.0021</t>
+  </si>
+  <si>
+    <t>0.9916,0.0018,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9966,0.0010,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9948,0.0011,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.3827,0.7326,0.0096,0.0063</t>
+  </si>
+  <si>
+    <t>0.4367,0.7076,0.0054,0.0005</t>
+  </si>
+  <si>
+    <t>0.5236,0.5296,0.0304,0.0010</t>
+  </si>
+  <si>
+    <t>0.4473,0.3217,0.3171,0.0045</t>
+  </si>
+  <si>
+    <t>0.9359,0.0818,0.0063,0.0014</t>
+  </si>
+  <si>
+    <t>0.9142,0.0365,0.0136,0.0250</t>
+  </si>
+  <si>
+    <t>0.9533,0.0557,0.0038,0.0020</t>
+  </si>
+  <si>
+    <t>0.9459,0.0572,0.0108,0.0011</t>
+  </si>
+  <si>
+    <t>0.0060,0.0355,0.9929,0.0003</t>
+  </si>
+  <si>
+    <t>0.9079,0.0499,0.0639,0.0012</t>
+  </si>
+  <si>
+    <t>0.0026,0.0012,0.9877,0.0220</t>
+  </si>
+  <si>
+    <t>0.0078,0.0474,0.9800,0.0034</t>
+  </si>
+  <si>
+    <t>0.1689,0.0386,0.8564,0.0027</t>
+  </si>
+  <si>
+    <t>0.0060,0.0171,0.9898,0.0008</t>
+  </si>
+  <si>
+    <t>0.0074,0.0057,0.9866,0.0022</t>
+  </si>
+  <si>
+    <t>0.0119,0.0059,0.9810,0.0019</t>
+  </si>
+  <si>
+    <t>0.1196,0.0195,0.8665,0.0187</t>
+  </si>
+  <si>
+    <t>0.1628,0.1240,0.7574,0.0045</t>
+  </si>
+  <si>
+    <t>0.1889,0.0143,0.8885,0.0007</t>
+  </si>
+  <si>
+    <t>0.4576,0.2835,0.3180,0.0142</t>
+  </si>
+  <si>
+    <t>0.5544,0.1569,0.3339,0.0054</t>
+  </si>
+  <si>
+    <t>0.3038,0.1330,0.5428,0.0008</t>
+  </si>
+  <si>
+    <t>0.3670,0.5045,0.0549,0.0037</t>
+  </si>
+  <si>
+    <t>0.6249,0.3327,0.0341,0.0201</t>
+  </si>
+  <si>
+    <t>0.5706,0.0585,0.4688,0.0084</t>
+  </si>
+  <si>
+    <t>0.5809,0.5897,0.0039,0.0010</t>
+  </si>
+  <si>
+    <t>0.8651,0.2598,0.0027,0.0007</t>
+  </si>
+  <si>
+    <t>0.9449,0.0929,0.0011,0.0011</t>
+  </si>
+  <si>
+    <t>0.9924,0.0023,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9438,0.0876,0.0036,0.0009</t>
+  </si>
+  <si>
+    <t>0.6645,0.0965,0.2475,0.0054</t>
+  </si>
+  <si>
+    <t>0.8391,0.0295,0.1270,0.0050</t>
+  </si>
+  <si>
+    <t>0.7361,0.0578,0.1155,0.0457</t>
+  </si>
+  <si>
+    <t>0.6256,0.0713,0.3107,0.0520</t>
+  </si>
+  <si>
+    <t>0.8222,0.0095,0.2060,0.0050</t>
+  </si>
+  <si>
+    <t>0.0197,0.0035,0.9650,0.0219</t>
+  </si>
+  <si>
+    <t>0.0569,0.0649,0.8805,0.0447</t>
+  </si>
+  <si>
+    <t>0.0204,0.0304,0.9343,0.0255</t>
+  </si>
+  <si>
+    <t>0.0855,0.0702,0.8997,0.0051</t>
+  </si>
+  <si>
+    <t>0.0348,0.0953,0.8805,0.0080</t>
+  </si>
+  <si>
+    <t>0.9945,0.0016,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9911,0.0051,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.9839,0.0066,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.9890,0.0065,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9830,0.0125,0.0010,0.0015</t>
+  </si>
+  <si>
+    <t>0.9838,0.0062,0.0004,0.0034</t>
+  </si>
+  <si>
+    <t>0.9789,0.0063,0.0005,0.0052</t>
+  </si>
+  <si>
+    <t>0.9957,0.0007,0.0003,0.0008</t>
+  </si>
+  <si>
+    <t>0.0249,0.0152,0.9514,0.0084</t>
+  </si>
+  <si>
+    <t>0.1147,0.2163,0.7759,0.0033</t>
+  </si>
+  <si>
+    <t>0.7734,0.0529,0.1033,0.0712</t>
+  </si>
+  <si>
+    <t>0.0271,0.0142,0.9739,0.0013</t>
+  </si>
+  <si>
+    <t>0.0083,0.0422,0.9515,0.0235</t>
+  </si>
+  <si>
+    <t>0.0322,0.2011,0.8390,0.0016</t>
+  </si>
+  <si>
+    <t>0.0046,0.0034,0.9924,0.0006</t>
+  </si>
+  <si>
+    <t>0.0656,0.0127,0.9394,0.0046</t>
+  </si>
+  <si>
+    <t>0.0134,0.0818,0.9614,0.0024</t>
+  </si>
+  <si>
+    <t>0.0158,0.0256,0.9519,0.0134</t>
+  </si>
+  <si>
+    <t>0.0780,0.0114,0.9475,0.0024</t>
+  </si>
+  <si>
+    <t>0.7658,0.0346,0.1908,0.0123</t>
+  </si>
+  <si>
+    <t>0.6162,0.0057,0.4765,0.0101</t>
+  </si>
+  <si>
+    <t>0.7936,0.0070,0.2534,0.0107</t>
+  </si>
+  <si>
+    <t>0.9889,0.0111,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9776,0.0328,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9975,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9694,0.0273,0.0018,0.0026</t>
+  </si>
+  <si>
+    <t>0.9941,0.0009,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9863,0.0108,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.9968,0.0009,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9687,0.0129,0.0006,0.0068</t>
+  </si>
+  <si>
+    <t>0.0346,0.0912,0.8957,0.0006</t>
+  </si>
+  <si>
+    <t>0.0010,0.0191,0.9932,0.0006</t>
+  </si>
+  <si>
+    <t>0.0130,0.1305,0.9462,0.0012</t>
+  </si>
+  <si>
+    <t>0.0727,0.0100,0.9293,0.0020</t>
+  </si>
+  <si>
+    <t>0.0021,0.0022,0.9948,0.0012</t>
+  </si>
+  <si>
+    <t>0.3019,0.0184,0.6183,0.0625</t>
+  </si>
+  <si>
+    <t>0.0279,0.0036,0.9754,0.0019</t>
+  </si>
+  <si>
+    <t>0.0993,0.0822,0.8339,0.0274</t>
+  </si>
+  <si>
+    <t>0.6152,0.0003,0.0141,0.2499</t>
+  </si>
+  <si>
+    <t>0.0053,0.0045,0.0018,0.9961</t>
+  </si>
+  <si>
+    <t>0.1283,0.0009,0.0027,0.9472</t>
+  </si>
+  <si>
+    <t>0.0026,0.0006,0.0006,0.9984</t>
+  </si>
+  <si>
+    <t>0.0057,0.0012,0.0003,0.9978</t>
+  </si>
+  <si>
+    <t>0.7367,0.0757,0.0171,0.1424</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2228,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2382,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2424,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2480,7 +2486,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2494,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2522,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2648,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,10 +2707,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,10 +2973,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,7 +3130,7 @@
         <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,10 +3141,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,10 +3505,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3550,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3600,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3614,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3656,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,10 +3673,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3698,7 +3704,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3712,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3838,7 +3844,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3922,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4006,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4034,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4118,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4160,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4356,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4370,7 +4376,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,10 +4625,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,10 +4709,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4832,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4860,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5042,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5168,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5182,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5196,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5448,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5518,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
